--- a/output/2026-09-07_06_Slovenia_Obalno-kraska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-07_06_Slovenia_Obalno-kraska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -506,7 +506,6 @@
           <t>BINMAT Bernetič in ostali, d.n.o.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Sežana (Lokev)</t>
@@ -571,7 +570,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rivenditore multi-brand di utensili manuali/professionali e forniture da officina (rappresenta Beta, Bosch professionale). Sede filiale: Kolodvorska cesta 1, 6000 Koper. Verificato tramite WebSearch (sito ufficiale tehimpex.si, pagine prodotto Beta).</t>
+          <t>Rivenditore multi-brand di utensili manuali/professionali e forniture da officina (rappresenta Beta, Bosch professionale). Sede filiale: Kolodvorska cesta 1, 6000 Koper. Verificato tramite WebSearch (sito ufficiale tehimpex.si, pagine prodotto Beta). [DUPLICATO — vedi anche: 2026-09-06_03_Slovenia_Koroska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -613,7 +612,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Punto vendita Topdom (gruppo Saint-Gobain): ferramenta, utensili, attrezzatura da lavoro, materiale edile. Sede: Komen 60, 6223 Komen. Verificato tramite topdom.si, saint-gobain.si, bizi.si.</t>
+          <t>Punto vendita Topdom (gruppo Saint-Gobain): ferramenta, utensili, attrezzatura da lavoro, materiale edile. Sede: Komen 60, 6223 Komen. Verificato tramite topdom.si, saint-gobain.si, bizi.si. [DUPLICATO — vedi anche: 2026-09-06_18_Slovenia_Primorsko-notranjska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -655,7 +654,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Filiale Topdom della stessa società con sede a Komen. Indirizzo: Vilharjeva cesta 24, 6250 Ilirska Bistrica (da non confondere con 'Agro Trgovina Magro' a Vilharjeva 33a, attività agricola separata della stessa azienda). Email di contatto condivisa con la sede di Komen, non è stata reperita un'email dedicata differente. Verificato tramite najdi.si/zemljevid, bizi.si.</t>
+          <t>Filiale Topdom della stessa società con sede a Komen. Indirizzo: Vilharjeva cesta 24, 6250 Ilirska Bistrica (da non confondere con 'Agro Trgovina Magro' a Vilharjeva 33a, attività agricola separata della stessa azienda). Email di contatto condivisa con la sede di Komen, non è stata reperita un'email dedicata differente. Verificato tramite najdi.si/zemljevid, bizi.si. [DUPLICATO — vedi anche: 2026-09-06_18_Slovenia_Primorsko-notranjska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
